--- a/assets/materials_template.xlsx
+++ b/assets/materials_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12210"/>
+    <workbookView windowWidth="24930" windowHeight="12210"/>
   </bookViews>
   <sheets>
     <sheet name="定检航化" sheetId="1" r:id="rId1"/>
@@ -303,7 +303,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="35">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -348,24 +348,6 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1056,152 +1038,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1244,34 +1226,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
@@ -1289,19 +1256,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1779,10 +1746,10 @@
       <c r="B9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="12">
         <v>1</v>
       </c>
       <c r="E9" s="12"/>
@@ -1795,10 +1762,10 @@
       <c r="B10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="12">
         <v>1</v>
       </c>
       <c r="E10" s="12"/>
@@ -1814,7 +1781,7 @@
       <c r="C11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="12">
         <v>1</v>
       </c>
       <c r="E11" s="12"/>
@@ -1823,16 +1790,16 @@
       <c r="H11" s="13"/>
     </row>
     <row r="12" ht="23" customHeight="1" spans="1:8">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="14" t="s">
         <v>27</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="12">
         <v>1</v>
       </c>
       <c r="E12" s="12"/>
@@ -1841,14 +1808,14 @@
       <c r="H12" s="13"/>
     </row>
     <row r="13" ht="23" customHeight="1" spans="1:8">
-      <c r="A13" s="16"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="12">
         <v>1</v>
       </c>
       <c r="E13" s="12"/>
@@ -1857,14 +1824,14 @@
       <c r="H13" s="13"/>
     </row>
     <row r="14" ht="23" customHeight="1" spans="1:8">
-      <c r="A14" s="16"/>
+      <c r="A14" s="14"/>
       <c r="B14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="12">
         <v>1</v>
       </c>
       <c r="E14" s="12"/>
@@ -1873,14 +1840,14 @@
       <c r="H14" s="13"/>
     </row>
     <row r="15" ht="23" customHeight="1" spans="1:8">
-      <c r="A15" s="16"/>
+      <c r="A15" s="14"/>
       <c r="B15" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="12">
         <v>1</v>
       </c>
       <c r="E15" s="12"/>
@@ -1889,14 +1856,14 @@
       <c r="H15" s="13"/>
     </row>
     <row r="16" ht="23" customHeight="1" spans="1:8">
-      <c r="A16" s="16"/>
+      <c r="A16" s="14"/>
       <c r="B16" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="12">
         <v>1</v>
       </c>
       <c r="E16" s="12"/>
@@ -1905,14 +1872,14 @@
       <c r="H16" s="13"/>
     </row>
     <row r="17" ht="29" customHeight="1" spans="1:8">
-      <c r="A17" s="16"/>
+      <c r="A17" s="14"/>
       <c r="B17" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="12">
         <v>1</v>
       </c>
       <c r="E17" s="12"/>
@@ -1921,69 +1888,69 @@
       <c r="H17" s="13"/>
     </row>
     <row r="18" ht="23" customHeight="1" spans="1:11">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="14" t="s">
         <v>40</v>
       </c>
       <c r="B18" s="12"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
       <c r="H18" s="13"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:11">
-      <c r="A19" s="16"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
       <c r="G19" s="12"/>
       <c r="H19" s="13"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="33"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="28"/>
     </row>
     <row r="20" ht="23" customHeight="1" spans="1:11">
-      <c r="A20" s="16"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
       <c r="G20" s="12"/>
       <c r="H20" s="13"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
     </row>
     <row r="21" ht="23" customHeight="1" spans="1:11">
-      <c r="A21" s="16"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
       <c r="G21" s="12"/>
       <c r="H21" s="13"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="33"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="28"/>
     </row>
     <row r="22" ht="23" customHeight="1" spans="1:8">
-      <c r="A22" s="16"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
       <c r="H22" s="13"/>
     </row>
     <row r="23" ht="23" customHeight="1" spans="1:8">
-      <c r="A23" s="16"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
@@ -1991,9 +1958,9 @@
       <c r="H23" s="13"/>
     </row>
     <row r="24" ht="23" customHeight="1" spans="1:8">
-      <c r="A24" s="16"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
+      <c r="A24" s="14"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -2001,29 +1968,29 @@
       <c r="H24" s="13"/>
     </row>
     <row r="25" ht="23" customHeight="1" spans="1:8">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F25" s="21" t="s">
+      <c r="F25" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G25" s="22"/>
-      <c r="H25" s="23"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="18"/>
     </row>
     <row r="26" ht="23" customHeight="1" spans="1:8">
-      <c r="A26" s="16"/>
+      <c r="A26" s="14"/>
       <c r="B26" s="12" t="s">
         <v>45</v>
       </c>
@@ -2033,13 +2000,13 @@
       <c r="D26" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="24"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="27"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="22"/>
     </row>
     <row r="27" ht="23" customHeight="1" spans="1:8">
-      <c r="A27" s="16"/>
+      <c r="A27" s="14"/>
       <c r="B27" s="12" t="s">
         <v>48</v>
       </c>
@@ -2049,13 +2016,13 @@
       <c r="D27" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="24"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="27"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="22"/>
     </row>
     <row r="28" ht="23" customHeight="1" spans="1:8">
-      <c r="A28" s="16"/>
+      <c r="A28" s="14"/>
       <c r="B28" s="12" t="s">
         <v>50</v>
       </c>
@@ -2065,52 +2032,52 @@
       <c r="D28" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="E28" s="24"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="27"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="22"/>
     </row>
     <row r="29" ht="23" customHeight="1" spans="1:8">
-      <c r="A29" s="16"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="27"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="22"/>
     </row>
     <row r="30" ht="23" customHeight="1" spans="1:8">
-      <c r="A30" s="16"/>
+      <c r="A30" s="14"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="27"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="22"/>
     </row>
     <row r="31" ht="23" customHeight="1" spans="1:8">
-      <c r="A31" s="16"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="27"/>
+      <c r="A31" s="14"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="22"/>
     </row>
     <row r="32" ht="52" customHeight="1" spans="1:8">
-      <c r="A32" s="28"/>
-      <c r="B32" s="29" t="s">
+      <c r="A32" s="23"/>
+      <c r="B32" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="30"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="25"/>
     </row>
     <row r="33" customHeight="1" spans="2:8">
       <c r="B33" s="1"/>
